--- a/users/template/entities_template.xlsx
+++ b/users/template/entities_template.xlsx
@@ -624,4 +624,217 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bebf88d6575d16559b5f30f0a2a701c1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" xmlns:ns3="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7261e384d67fa0b6a688911c7473044a" ns2:_="" ns3:_="">
+    <xsd:import namespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
+    <xsd:import namespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8f7c344f-19d0-4f45-b23a-2df2b546d212" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4dc7bc77-2376-40bf-86a0-4a9e9b5c2537}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34CFBDED-E80C-4D17-B26F-FFFD8C7E3DF3}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BEDC57C-EA82-4DA7-976E-B4105A1E62C4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E000561-2D82-4D87-AEA3-FC42CED788DE}"/>
 </file>
--- a/users/template/entities_template.xlsx
+++ b/users/template/entities_template.xlsx
@@ -1,36 +1,140 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_07CE9206A3E7EDD442704369F19EB289068DE7C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE78578-4606-425D-ABC3-E36A203B5DA3}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entities" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="huong_dan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="entities" sheetId="1" r:id="rId1"/>
+    <sheet name="meta" sheetId="2" r:id="rId2"/>
+    <sheet name="huong_dan" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>tickers</t>
+  </si>
+  <si>
+    <t>etfs</t>
+  </si>
+  <si>
+    <t>indices</t>
+  </si>
+  <si>
+    <t>exchanges</t>
+  </si>
+  <si>
+    <t>industries</t>
+  </si>
+  <si>
+    <t>entities</t>
+  </si>
+  <si>
+    <t>HPG</t>
+  </si>
+  <si>
+    <t>E1VFVN30</t>
+  </si>
+  <si>
+    <t>VNINDEX</t>
+  </si>
+  <si>
+    <t>HOSE</t>
+  </si>
+  <si>
+    <t>THEP</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Cách nhập</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Mỗi cột trong sheet 'entities' là 1 nhóm; nhập MỖI giá trị 1 dòng.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>tickers/etfs/indices/exchanges: nhập MÃ (vd HPG, FPT, VNINDEX, HOSE).</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>industries: nhập MÃ ngành GICS (vd THEP, NGAN_HANG) — dùng code, KHÔNG dùng tên.</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>entities: (nâng cao) entity_id nguyên bản dạng TYPE:CODE (vd TICKER:HPG).</t>
+  </si>
+  <si>
+    <t>Tra mã</t>
+  </si>
+  <si>
+    <t>Xem danh sách hợp lệ trong data/entities/entities.xlsx (sheet Securities/Industries/...).</t>
+  </si>
+  <si>
+    <t>Bật/tắt</t>
+  </si>
+  <si>
+    <t>Bật/tắt user ở users/input/manifest.yaml (vắng tên = mặc định BẬT).</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,80 +153,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -410,76 +455,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>tickers</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>etfs</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>indices</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>exchanges</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>industries</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>entities</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HPG</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>E1VFVN30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>VNINDEX</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HOSE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>THEP</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D200" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"HOSE,HNX,UPCOM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -488,41 +507,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -530,95 +535,64 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Cách nhập</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Mỗi cột trong sheet 'entities' là 1 nhóm; nhập MỖI giá trị 1 dòng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>tickers/etfs/indices/exchanges: nhập MÃ (vd HPG, FPT, VNINDEX, HOSE).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>industries: nhập MÃ ngành GICS (vd THEP, NGAN_HANG) — dùng code, KHÔNG dùng tên.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>entities: (nâng cao) entity_id nguyên bản dạng TYPE:CODE (vd TICKER:HPG).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tra mã</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Xem danh sách hợp lệ trong data/entities/entities.xlsx (sheet Securities/Industries/...).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bật/tắt</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bật/tắt user ở users/input/manifest.yaml (vắng tên = mặc định BẬT).</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -627,6 +601,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bebf88d6575d16559b5f30f0a2a701c1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" xmlns:ns3="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7261e384d67fa0b6a688911c7473044a" ns2:_="" ns3:_="">
     <xsd:import namespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
@@ -807,28 +801,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34CFBDED-E80C-4D17-B26F-FFFD8C7E3DF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E000561-2D82-4D87-AEA3-FC42CED788DE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -836,5 +810,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E000561-2D82-4D87-AEA3-FC42CED788DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34CFBDED-E80C-4D17-B26F-FFFD8C7E3DF3}"/>
 </file>
--- a/users/template/entities_template.xlsx
+++ b/users/template/entities_template.xlsx
@@ -1,140 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_07CE9206A3E7EDD442704369F19EB289068DE7C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEE78578-4606-425D-ABC3-E36A203B5DA3}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="entities" sheetId="1" r:id="rId1"/>
-    <sheet name="meta" sheetId="2" r:id="rId2"/>
-    <sheet name="huong_dan" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entities" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="huong_dan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>tickers</t>
-  </si>
-  <si>
-    <t>etfs</t>
-  </si>
-  <si>
-    <t>indices</t>
-  </si>
-  <si>
-    <t>exchanges</t>
-  </si>
-  <si>
-    <t>industries</t>
-  </si>
-  <si>
-    <t>entities</t>
-  </si>
-  <si>
-    <t>HPG</t>
-  </si>
-  <si>
-    <t>E1VFVN30</t>
-  </si>
-  <si>
-    <t>VNINDEX</t>
-  </si>
-  <si>
-    <t>HOSE</t>
-  </si>
-  <si>
-    <t>THEP</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>Cách nhập</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Mỗi cột trong sheet 'entities' là 1 nhóm; nhập MỖI giá trị 1 dòng.</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>tickers/etfs/indices/exchanges: nhập MÃ (vd HPG, FPT, VNINDEX, HOSE).</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>industries: nhập MÃ ngành GICS (vd THEP, NGAN_HANG) — dùng code, KHÔNG dùng tên.</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>entities: (nâng cao) entity_id nguyên bản dạng TYPE:CODE (vd TICKER:HPG).</t>
-  </si>
-  <si>
-    <t>Tra mã</t>
-  </si>
-  <si>
-    <t>Xem danh sách hợp lệ trong data/entities/entities.xlsx (sheet Securities/Industries/...).</t>
-  </si>
-  <si>
-    <t>Bật/tắt</t>
-  </si>
-  <si>
-    <t>Bật/tắt user ở users/input/manifest.yaml (vắng tên = mặc định BẬT).</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -153,21 +49,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -455,50 +410,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tickers</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>etfs</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>indices</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>exchanges</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>industries</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>nations</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>themes</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>macro</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>institutions</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>entities</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>E1VFVN30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>VNINDEX</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HOSE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>THEP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>LAI_SUAT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRAI_PHIEU</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NHNN</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D200" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"HOSE,HNX,UPCOM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -507,27 +538,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -535,64 +580,143 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cách nhập</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mỗi cột trong sheet 'entities' là 1 nhóm; nhập MỖI giá trị 1 dòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tickers/etfs/indices/exchanges: nhập MÃ (vd HPG, FPT, VNINDEX, HOSE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>industries: nhập MÃ ngành GICS (vd THEP, NGAN_HANG, QUY) — tra cứu sheet 'Industries'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nations: nhập MÃ quốc gia/địa chính trị (vd MY, TRUNG_QUOC, EU) — tra cứu sheet 'Nations'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>themes: nhập MÃ chủ đề vĩ mô (vd LAI_SUAT, TY_GIA, LAM_PHAT, DAU_TU_CONG) — tra cứu sheet 'Themes'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>assets: nhập MÃ loại tài sản (vd TRAI_PHIEU, CO_PHIEU, VANG, DAU_THO) — tra cứu sheet 'Assets'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>institutions: nhập MÃ định chế (vd NHNN, UBCKNN, FED, ECB) — tra cứu sheet 'Institutions'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>entities: (nâng cao) entity_id nguyên bản dạng TYPE:CODE (vd TICKER:HPG).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tra mã</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Xem toàn bộ danh mục mã hợp lệ trong data/entities/entities.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bật/tắt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bật/tắt user ở users/input/manifest.yaml (vắng tên = mặc định BẬT).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -601,26 +725,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010088BB270C8F5FC24BA49AFFE556196667" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bebf88d6575d16559b5f30f0a2a701c1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c36903d5-5ed0-4454-a196-b1a2f9ebaa03" xmlns:ns3="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7261e384d67fa0b6a688911c7473044a" ns2:_="" ns3:_="">
     <xsd:import namespace="c36903d5-5ed0-4454-a196-b1a2f9ebaa03"/>
@@ -801,14 +905,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c36903d5-5ed0-4454-a196-b1a2f9ebaa03">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="540cf7b3-6f7a-4cd3-95f1-edd8c1c86d9a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E000561-2D82-4D87-AEA3-FC42CED788DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA90B2DE-21A6-4142-ACDF-E20CFA6FB86E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BEDC57C-EA82-4DA7-976E-B4105A1E62C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE51C466-9038-4869-BAF8-97AEE2833AB7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34CFBDED-E80C-4D17-B26F-FFFD8C7E3DF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDDC93DC-02A6-47EF-A283-76DFEFFB9F3B}"/>
 </file>